--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484195_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484195_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.5508</v>
+        <v>0.8748</v>
       </c>
       <c r="E2" t="n">
-        <v>1.5216</v>
+        <v>0.7054</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0292</v>
+        <v>0.1695</v>
       </c>
       <c r="G2" t="n">
         <v>0.5613</v>
@@ -610,13 +610,13 @@
         <v>0.1984</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0571</v>
+        <v>0.3812</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3094</v>
+        <v>0.4932</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2523</v>
+        <v>-0.112</v>
       </c>
       <c r="V2" t="n">
         <v>-0.266</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. MARBÀ RECASENS</t>
+          <t>M. ALIAGA CHECA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5958</v>
+        <v>0.583</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6607</v>
+        <v>0.8236</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0649</v>
+        <v>-0.2405</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.3223</v>
+        <v>-0.8322000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.3831</v>
+        <v>2.8381</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.9393</v>
+        <v>-3.6703</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.66</v>
+        <v>1.4025</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0202</v>
+        <v>3.3627</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6802</v>
+        <v>-1.9603</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.6623</v>
+        <v>-2.2346</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4032</v>
+        <v>-0.5246</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2591</v>
+        <v>-1.71</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3968</v>
+        <v>1.1903</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3968</v>
+        <v>2.1822</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5214</v>
+        <v>-0.7156</v>
       </c>
       <c r="T3" t="n">
-        <v>1.3207</v>
+        <v>-0.1189</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2006</v>
+        <v>-0.5967</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.9405</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.532</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.4085</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2863</v>
+        <v>0.2554</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1486</v>
+        <v>-0.1348</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1377</v>
+        <v>0.3902</v>
       </c>
       <c r="G4" t="n">
         <v>-0.9181</v>
@@ -766,13 +766,13 @@
         <v>1.3887</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6649</v>
+        <v>-0.6958</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0452</v>
+        <v>-0.3287</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6196</v>
+        <v>-0.3671</v>
       </c>
       <c r="V4" t="n">
         <v>1.4724</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. ALIAGA CHECA</t>
+          <t>J. MARBÀ RECASENS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1462</v>
+        <v>-0.1122</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2907</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4369</v>
+        <v>-0.121</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.8322000000000001</v>
+        <v>-1.3223</v>
       </c>
       <c r="H5" t="n">
-        <v>2.8381</v>
+        <v>-0.3831</v>
       </c>
       <c r="I5" t="n">
-        <v>-3.6703</v>
+        <v>-0.9393</v>
       </c>
       <c r="J5" t="n">
-        <v>1.4025</v>
+        <v>-0.66</v>
       </c>
       <c r="K5" t="n">
-        <v>3.3627</v>
+        <v>0.0202</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.9603</v>
+        <v>-0.6802</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.2346</v>
+        <v>-0.6623</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5246</v>
+        <v>-0.4032</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.71</v>
+        <v>-0.2591</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1903</v>
+        <v>0.3968</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1822</v>
+        <v>0.3968</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.4448</v>
+        <v>0.8134</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6518</v>
+        <v>0.6689000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.793</v>
+        <v>0.1445</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9405</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.532</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.4085</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4396</v>
+        <v>-0.1514</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5662</v>
+        <v>-0.3621</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1266</v>
+        <v>0.2107</v>
       </c>
       <c r="G6" t="n">
         <v>-0.5694</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1298</v>
+        <v>0.418</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0737</v>
+        <v>0.2778</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0561</v>
+        <v>0.1403</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. BERNADÍ VALLS</t>
+          <t>M. BENITO MULLERAT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.1581</v>
+        <v>-1.915</v>
       </c>
       <c r="E7" t="n">
-        <v>-4.4094</v>
+        <v>-1.7289</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2513</v>
+        <v>-0.1861</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.4004</v>
+        <v>-1.83</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.6026</v>
+        <v>0.292</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2022</v>
+        <v>-2.1221</v>
       </c>
       <c r="J7" t="n">
-        <v>-3.3099</v>
+        <v>0.2095</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.3501</v>
+        <v>0.8871</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0402</v>
+        <v>-0.6776</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0905</v>
+        <v>-2.0395</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2525</v>
+        <v>-0.5951</v>
       </c>
       <c r="O7" t="n">
-        <v>0.162</v>
+        <v>-1.4444</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3968</v>
+        <v>0.1984</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3887</v>
+        <v>2.1822</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7742</v>
+        <v>-0.2834</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1076</v>
+        <v>0.0454</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8818</v>
+        <v>-0.3288</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0713</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0713</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. FONS TEIXIDO</t>
+          <t>M. BERNADÍ VALLS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.4478</v>
+        <v>-2.4988</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.3534</v>
+        <v>-4.245</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0944</v>
+        <v>1.7463</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.9885</v>
+        <v>-3.4004</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.6683</v>
+        <v>-3.6026</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.3202</v>
+        <v>0.2022</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.3951</v>
+        <v>-3.3099</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5995</v>
+        <v>-3.3501</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7956</v>
+        <v>0.0402</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.5934</v>
+        <v>-0.0905</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.0688</v>
+        <v>-0.2525</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5247000000000001</v>
+        <v>0.162</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.7935</v>
+        <v>0.3968</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1903</v>
+        <v>1.3887</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3343</v>
+        <v>0.4336</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7596000000000001</v>
+        <v>0.0568</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5747</v>
+        <v>0.3768</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.0713</v>
       </c>
       <c r="W8" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.266</v>
+        <v>0.0713</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. BENITO MULLERAT</t>
+          <t>C. FONS TEIXIDO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.8865</v>
+        <v>-2.9517</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.3638</v>
+        <v>-2.8012</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5228</v>
+        <v>-0.1505</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.83</v>
+        <v>-2.9885</v>
       </c>
       <c r="H9" t="n">
-        <v>0.292</v>
+        <v>-1.6683</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.1221</v>
+        <v>-1.3202</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2095</v>
+        <v>-1.3951</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8871</v>
+        <v>-0.5995</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6776</v>
+        <v>-0.7956</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.0395</v>
+        <v>-1.5934</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5951</v>
+        <v>-1.0688</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.4444</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1984</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.9838</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1822</v>
+        <v>1.1903</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.2549</v>
+        <v>0.8304</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5894</v>
+        <v>0.3118</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6655</v>
+        <v>0.5185999999999999</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.9732</v>
+        <v>-3.0715</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4468</v>
+        <v>-1.1804</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5264</v>
+        <v>-1.8911</v>
       </c>
       <c r="G10" t="n">
         <v>-3.5033</v>
@@ -1234,13 +1234,13 @@
         <v>2.3806</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2046</v>
+        <v>0.1063</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.408</v>
+        <v>-0.1416</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6126</v>
+        <v>0.2479</v>
       </c>
       <c r="V10" t="n">
         <v>-0.0713</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.7688</v>
+        <v>-3.2601</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.8478</v>
+        <v>-1.4794</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.921</v>
+        <v>-1.7807</v>
       </c>
       <c r="G11" t="n">
         <v>-2.5539</v>
@@ -1312,13 +1312,13 @@
         <v>0.3968</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4052</v>
+        <v>0.1035</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4874</v>
+        <v>-0.119</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0822</v>
+        <v>0.2224</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2065</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.3667</v>
+        <v>-4.2001</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.7148</v>
+        <v>-3.3237</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6519</v>
+        <v>-0.8764</v>
       </c>
       <c r="G12" t="n">
         <v>-2.879</v>
@@ -1390,13 +1390,13 @@
         <v>1.7855</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.246</v>
+        <v>-0.0794</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5894</v>
+        <v>-0.1983</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3434</v>
+        <v>0.1189</v>
       </c>
       <c r="V12" t="n">
         <v>0.9405</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.7902</v>
+        <v>-6.1616</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.7824</v>
+        <v>-5.2099</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.0078</v>
+        <v>-0.9517</v>
       </c>
       <c r="G13" t="n">
         <v>-5.6714</v>
@@ -1468,13 +1468,13 @@
         <v>1.3887</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5237000000000001</v>
+        <v>0.1049</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7254</v>
+        <v>-0.153</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2017</v>
+        <v>0.2579</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-23.5442</v>
+        <v>-22.6092</v>
       </c>
       <c r="E14" t="n">
-        <v>-19.863</v>
+        <v>-18.9276</v>
       </c>
       <c r="F14" t="n">
         <v>-3.6813</v>
@@ -1513,7 +1513,7 @@
         <v>-25.9072</v>
       </c>
       <c r="H14" t="n">
-        <v>-6.4741</v>
+        <v>-6.474099999999999</v>
       </c>
       <c r="I14" t="n">
         <v>-19.4332</v>
@@ -1546,13 +1546,13 @@
         <v>14.8789</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4819</v>
+        <v>1.4171</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1408000000000006</v>
+        <v>0.7944000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6226999999999999</v>
+        <v>0.6227</v>
       </c>
       <c r="V14" t="n">
         <v>1.8809</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.358000000000001</v>
+        <v>9.018700000000001</v>
       </c>
       <c r="E15" t="n">
         <v>5.8033</v>
       </c>
       <c r="F15" t="n">
-        <v>2.5548</v>
+        <v>3.2154</v>
       </c>
       <c r="G15" t="n">
         <v>6.5776</v>
@@ -1624,13 +1624,13 @@
         <v>1.9838</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2908</v>
+        <v>0.3698</v>
       </c>
       <c r="T15" t="n">
         <v>0.1928</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4836</v>
+        <v>0.1771</v>
       </c>
       <c r="V15" t="n">
         <v>1.2777</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>7.5838</v>
+        <v>7.4214</v>
       </c>
       <c r="E16" t="n">
-        <v>2.8053</v>
+        <v>2.2951</v>
       </c>
       <c r="F16" t="n">
-        <v>4.7785</v>
+        <v>5.1263</v>
       </c>
       <c r="G16" t="n">
         <v>4.9827</v>
@@ -1702,13 +1702,13 @@
         <v>2.1822</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6172</v>
+        <v>0.4548</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4252</v>
+        <v>-0.0849</v>
       </c>
       <c r="U16" t="n">
-        <v>0.192</v>
+        <v>0.5397999999999999</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>6.9858</v>
+        <v>6.6032</v>
       </c>
       <c r="E17" t="n">
-        <v>4.0752</v>
+        <v>3.565</v>
       </c>
       <c r="F17" t="n">
-        <v>2.9106</v>
+        <v>3.0382</v>
       </c>
       <c r="G17" t="n">
         <v>3.3672</v>
@@ -1780,13 +1780,13 @@
         <v>1.9838</v>
       </c>
       <c r="S17" t="n">
-        <v>1.0316</v>
+        <v>0.649</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6859</v>
+        <v>0.1758</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3456</v>
+        <v>0.4732</v>
       </c>
       <c r="V17" t="n">
         <v>0.6032</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.2358</v>
+        <v>5.3378</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4955</v>
+        <v>2.4137</v>
       </c>
       <c r="F18" t="n">
-        <v>2.7404</v>
+        <v>2.9241</v>
       </c>
       <c r="G18" t="n">
         <v>4.0625</v>
@@ -1858,13 +1858,13 @@
         <v>2.1822</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3424</v>
+        <v>0.7595</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9238</v>
+        <v>-0.0056</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5814</v>
+        <v>0.7651</v>
       </c>
       <c r="V18" t="n">
         <v>-0.6745</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.7757</v>
+        <v>3.6838</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8816000000000001</v>
+        <v>-0.2694</v>
       </c>
       <c r="F19" t="n">
-        <v>3.6573</v>
+        <v>3.9532</v>
       </c>
       <c r="G19" t="n">
         <v>4.7498</v>
@@ -1936,13 +1936,13 @@
         <v>1.5871</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8514</v>
+        <v>0.0567</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9975000000000001</v>
+        <v>-0.3853</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1461</v>
+        <v>0.442</v>
       </c>
       <c r="V19" t="n">
         <v>0.266</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.474</v>
+        <v>2.8303</v>
       </c>
       <c r="E20" t="n">
         <v>1.1032</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3708</v>
+        <v>1.727</v>
       </c>
       <c r="G20" t="n">
         <v>2.4459</v>
@@ -2014,13 +2014,13 @@
         <v>1.1903</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6978</v>
+        <v>-0.3415</v>
       </c>
       <c r="T20" t="n">
         <v>-0.3117</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3861</v>
+        <v>-0.0298</v>
       </c>
       <c r="V20" t="n">
         <v>-0.266</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B. BORRERO PERLAZA</t>
+          <t>A. MONTALVO PEREZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5577</v>
+        <v>-0.1685</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1062</v>
+        <v>-0.8358</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4516</v>
+        <v>0.6674</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.4922</v>
+        <v>1.0716</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.6348</v>
+        <v>-0.4183</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1425</v>
+        <v>1.4899</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3725</v>
+        <v>0.4965</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.3725</v>
+        <v>0.3735</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.123</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1198</v>
+        <v>0.5750999999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2623</v>
+        <v>-0.7917999999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1425</v>
+        <v>1.3669</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.5952</v>
+        <v>0.1984</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9919</v>
+        <v>-1.1903</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3968</v>
+        <v>1.3887</v>
       </c>
       <c r="S21" t="n">
-        <v>1.7164</v>
+        <v>0.034</v>
       </c>
       <c r="T21" t="n">
-        <v>1.5418</v>
+        <v>-0.408</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1746</v>
+        <v>0.442</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.0713</v>
+        <v>-1.4724</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.0713</v>
+        <v>0.266</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.7384</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. MONTALVO PEREZ</t>
+          <t>B. BORRERO PERLAZA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5324</v>
+        <v>-0.2942</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.0399</v>
+        <v>-0.9141</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5075</v>
+        <v>0.6199</v>
       </c>
       <c r="G22" t="n">
-        <v>1.0716</v>
+        <v>-0.4922</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4183</v>
+        <v>-0.6348</v>
       </c>
       <c r="I22" t="n">
-        <v>1.4899</v>
+        <v>0.1425</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4965</v>
+        <v>-0.3725</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3735</v>
+        <v>-0.3725</v>
       </c>
       <c r="L22" t="n">
-        <v>0.123</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.5750999999999999</v>
+        <v>-0.1198</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7917999999999999</v>
+        <v>-0.2623</v>
       </c>
       <c r="O22" t="n">
-        <v>1.3669</v>
+        <v>0.1425</v>
       </c>
       <c r="P22" t="n">
-        <v>0.1984</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1903</v>
+        <v>-0.9919</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3887</v>
+        <v>0.3968</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3299</v>
+        <v>0.8643999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6121</v>
+        <v>0.5215</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2822</v>
+        <v>0.3429</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.4724</v>
+        <v>-0.0713</v>
       </c>
       <c r="W22" t="n">
-        <v>0.266</v>
+        <v>-0.0713</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.7384</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. NINOT PEDROSA</t>
+          <t>J. GAVALDA GUILLEN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.1318</v>
+        <v>-0.7492</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.575</v>
+        <v>-2.4873</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4432</v>
+        <v>1.7382</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.145</v>
+        <v>0.0589</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1206</v>
+        <v>-0.0862</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2656</v>
+        <v>0.1451</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6399</v>
+        <v>-0.5768</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0403</v>
+        <v>0.1008</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6802</v>
+        <v>-0.6776</v>
       </c>
       <c r="M23" t="n">
-        <v>0.4949</v>
+        <v>0.6358</v>
       </c>
       <c r="N23" t="n">
-        <v>0.08019999999999999</v>
+        <v>-0.187</v>
       </c>
       <c r="O23" t="n">
-        <v>0.4146</v>
+        <v>0.8227</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.7935</v>
+        <v>-1.1903</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R23" t="n">
-        <v>0.1984</v>
+        <v>0.7935</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1933</v>
+        <v>0.1162</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0567</v>
+        <v>-0.1926</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.25</v>
+        <v>0.3089</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. GAVALDA GUILLEN</t>
+          <t>M. NINOT PEDROSA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.1896</v>
+        <v>-1.0137</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.4873</v>
+        <v>-1.6771</v>
       </c>
       <c r="F24" t="n">
-        <v>1.2978</v>
+        <v>0.6634</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0589</v>
+        <v>-0.145</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.0862</v>
+        <v>0.1206</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1451</v>
+        <v>-0.2656</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.5768</v>
+        <v>-0.6399</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1008</v>
+        <v>0.0403</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6776</v>
+        <v>-0.6802</v>
       </c>
       <c r="M24" t="n">
-        <v>0.6358</v>
+        <v>0.4949</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.187</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>0.8227</v>
+        <v>0.4146</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.1903</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R24" t="n">
-        <v>0.7935</v>
+        <v>0.1984</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3242</v>
+        <v>-0.0751</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1926</v>
+        <v>-0.0453</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1316</v>
+        <v>-0.0298</v>
       </c>
       <c r="V24" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.5729</v>
+        <v>-5.7244</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.7233</v>
+        <v>-5.3152</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.8496</v>
+        <v>-0.4092</v>
       </c>
       <c r="G25" t="n">
         <v>-0.7717000000000001</v>
@@ -2404,13 +2404,13 @@
         <v>0.9919</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.8174</v>
+        <v>0.0312</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4874</v>
+        <v>-0.0793</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3299</v>
+        <v>0.1105</v>
       </c>
       <c r="V25" t="n">
         <v>-1.8097</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>23.5441</v>
+        <v>26.9452</v>
       </c>
       <c r="E26" t="n">
-        <v>3.6816</v>
+        <v>3.681400000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>19.8629</v>
+        <v>23.2639</v>
       </c>
       <c r="G26" t="n">
         <v>25.90730000000001</v>
@@ -2482,13 +2482,13 @@
         <v>14.8787</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.482</v>
+        <v>2.919</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.6227</v>
+        <v>-0.6225999999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>0.1407</v>
+        <v>3.5419</v>
       </c>
       <c r="V26" t="n">
         <v>-1.881</v>
